--- a/docs/verification/files/rocscience/joints/rj017.xlsx
+++ b/docs/verification/files/rocscience/joints/rj017.xlsx
@@ -3374,7 +3374,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>

--- a/docs/verification/files/rocscience/joints/rj017.xlsx
+++ b/docs/verification/files/rocscience/joints/rj017.xlsx
@@ -13179,20 +13179,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>21.95</v>
-      </c>
-      <c r="C3" s="3">
-        <v>31.8</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>7.6864664555</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
